--- a/Book 1.xlsx
+++ b/Book 1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89435035-C7EC-45A3-BEAB-034581406635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96EBB453-33AB-4DC7-9805-5D3119E6191E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,7 +13,6 @@
     <sheet name="TAM" sheetId="3" r:id="rId3"/>
     <sheet name="SAM_SOM" sheetId="1" r:id="rId4"/>
     <sheet name="PROJECTIONS" sheetId="6" r:id="rId5"/>
-    <sheet name="Dashboard" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -2356,7 +2355,7 @@
         <v>131</v>
       </c>
       <c r="C6">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -2556,27 +2555,27 @@
       </c>
       <c r="D16">
         <f>C16*(1+$C$6+$C$5)</f>
-        <v>2021825.38</v>
+        <v>1968148.5999999999</v>
       </c>
       <c r="E16">
         <f>D16*(1+$C$6+$C$5)</f>
-        <v>2284662.6793999998</v>
+        <v>2164963.4599999995</v>
       </c>
       <c r="F16">
         <f>E16*(1+$C$6+$C$5)</f>
-        <v>2581668.8277219995</v>
+        <v>2381459.8059999989</v>
       </c>
       <c r="G16">
         <f>F16*(1+$C$6+$C$5)</f>
-        <v>2917285.775325859</v>
+        <v>2619605.7865999984</v>
       </c>
       <c r="H16">
         <f>G16*(1+$C$6+$C$5)</f>
-        <v>3296532.9261182202</v>
+        <v>2881566.365259998</v>
       </c>
       <c r="I16">
         <f>H16*(1+$C$6+$C$5)</f>
-        <v>3725082.2065135883</v>
+        <v>3169723.0017859973</v>
       </c>
     </row>
     <row r="17" spans="2:9">
@@ -2686,27 +2685,27 @@
       </c>
       <c r="D21" s="23">
         <f>C23*(1+$C$6+$C$5)*(1+$C$7)</f>
-        <v>83218332640.799988</v>
+        <v>81008996375.999985</v>
       </c>
       <c r="E21" s="23">
         <f>D21*(1+$C$6+$C$5)*(1+$C$7)</f>
-        <v>92155981566.42189</v>
+        <v>87327698093.327972</v>
       </c>
       <c r="F21" s="23">
         <f>E21*(1+$C$6+$C$5)*(1+$C$7)</f>
-        <v>102053533986.65559</v>
+        <v>94139258544.607529</v>
       </c>
       <c r="G21" s="23">
         <f>F21*(1+$C$6+$C$5)*(1+$C$7)</f>
-        <v>113014083536.82239</v>
+        <v>101482120711.0869</v>
       </c>
       <c r="H21" s="23">
         <f t="shared" ref="F21:I21" si="4">G21*(1+$C$6+$C$5)*(1+$C$7)</f>
-        <v>125151796108.67709</v>
+        <v>109397726126.55165</v>
       </c>
       <c r="I21" s="23">
         <f t="shared" si="4"/>
-        <v>138593099010.74902</v>
+        <v>117930748764.42267</v>
       </c>
     </row>
     <row r="22" spans="2:9">
@@ -2817,7 +2816,7 @@
       </c>
       <c r="C27">
         <f>I16</f>
-        <v>3725082.2065135883</v>
+        <v>3169723.0017859973</v>
       </c>
       <c r="D27">
         <f>I17</f>
@@ -2834,7 +2833,7 @@
       </c>
       <c r="C28" s="23">
         <f>I21</f>
-        <v>138593099010.74902</v>
+        <v>117930748764.42267</v>
       </c>
       <c r="D28" s="23">
         <f>I22</f>
@@ -2851,7 +2850,7 @@
       </c>
       <c r="C29">
         <f>C27/C26</f>
-        <v>0.16267230655706427</v>
+        <v>0.13842007323916189</v>
       </c>
       <c r="D29">
         <f>D27/D26</f>
@@ -2868,16 +2867,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A131D2-0403-47E3-866F-AB128F9F3706}">
-  <sheetPr>
-    <tabColor theme="3" tint="0.499984740745262"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>